--- a/teacher_forms/001_student_survey--teacher_forms.xlsx
+++ b/teacher_forms/001_student_survey--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>course_materials</t>
+          <t>teacher_resources</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What are the teacher's materials and resources useful?</t>
+          <t>What are the teacher's materials and resources useful for you?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>facilities_satisfaction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What are your thoughts about the facilities?</t>
+          <t>How satisfied are you with the facilities?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How would you rate your instructor?</t>
+          <t>How would you rate your instructor's quality?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>curriculum_satisfaction</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What are your thoughts about the facilities?</t>
+          <t>What are your thoughts about the curriculum?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>curriculum</t>
+          <t>feedback_and_assessment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What are your thoughts about the curriculum?</t>
+          <t>How satisfied are you with the instructor's feedback and assessment?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>communication_style</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>How would you rate the instructor's communication style?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>teaching_pace</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What are your thoughts about the facilities?</t>
+          <t>How would you rate the instructor's teaching pace?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>overall_course_experience</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What are your thoughts about the facilities?</t>
+          <t>How satisfied are you with the overall course experience?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>course_materials</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>How would you rate the overall quality of the course materials?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>instructor_quality_important</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>How important is it to have an instructor with high quality?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>facilities_important</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>How important is it to have good facilities?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>communication_important</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>How important is it to have effective communication?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>course_content</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>How satisfied are you with the course content?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>course_organization</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>How satisfied are you with the way the course is organized?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>instructor_availability</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>How satisfied are you with the instructor's availability for office hours?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>student_interaction</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>How satisfied are you with student interaction with each other and the instructor?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>instructor_help</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>How satisfied are you with the instructor's help?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,44 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>overall_rating</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>What would you rate the course overall?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Facilities</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -963,9 +940,9 @@
   <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -988,68 +965,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>course_materials_choices</t>
+          <t>teacher_resources_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>course_materials_choices</t>
+          <t>teacher_resources_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>facilities_satisfaction_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>facilities_satisfaction_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1090,544 +1067,544 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>curriculum_satisfaction_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>curriculum_satisfaction_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>curriculum_choices</t>
+          <t>feedback_and_assessment_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>curriculum_choices</t>
+          <t>feedback_and_assessment_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>teaching_pace_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>teaching_pace_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>overall_course_experience_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>overall_course_experience_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>course_materials_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>course_materials_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>instructor_quality_important_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>instructor_quality_important_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>important</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>facilities_important_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>facilities_important_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>important</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>communication_important_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>communication_important_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>important</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>course_content_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>course_content_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>course_organization_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>course_organization_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>instructor_availability_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>instructor_availability_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>student_interaction_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>student_interaction_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>instructor_help_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>instructor_help_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>overall_rating_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>overall_rating_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>overall_rating_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>overall_rating_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
